--- a/app/src/main/assets/methodmesh/odk_templates/conversions/example_odk_showcase_conversion_calculate.xlsx
+++ b/app/src/main/assets/methodmesh/odk_templates/conversions/example_odk_showcase_conversion_calculate.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Rf49dcb123cf44eca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R6e470c0f78824ed2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Re16257f2302f4901"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R949b36c5723d4d64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R3cd95fd4c3524b94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R002ea2a8e0324eff"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -336,15 +336,15 @@
       <x:c r="D2" s="8" t="str">
         <x:v>Convert units or run a general calculation</x:v>
       </x:c>
-      <x:c r="E2" s="8" t="str"/>
-      <x:c r="F2" s="8" t="str"/>
-      <x:c r="G2" s="8" t="str"/>
-      <x:c r="H2" s="8" t="str"/>
-      <x:c r="I2" s="8" t="str"/>
-      <x:c r="J2" s="8" t="str"/>
-      <x:c r="K2" s="8" t="str"/>
-      <x:c r="L2" s="8" t="str"/>
-      <x:c r="M2" s="8" t="str"/>
+      <x:c r="E2" s="8"/>
+      <x:c r="F2" s="8"/>
+      <x:c r="G2" s="8"/>
+      <x:c r="H2" s="8"/>
+      <x:c r="I2" s="8"/>
+      <x:c r="J2" s="8"/>
+      <x:c r="K2" s="8"/>
+      <x:c r="L2" s="8"/>
+      <x:c r="M2" s="8"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="8" t="str">
@@ -362,13 +362,13 @@
       <x:c r="E3" s="8" t="str">
         <x:v>field-list</x:v>
       </x:c>
-      <x:c r="F3" s="8" t="str"/>
-      <x:c r="G3" s="8" t="str"/>
-      <x:c r="H3" s="8" t="str"/>
-      <x:c r="I3" s="8" t="str"/>
-      <x:c r="J3" s="8" t="str"/>
-      <x:c r="K3" s="8" t="str"/>
-      <x:c r="L3" s="8" t="str"/>
+      <x:c r="F3" s="8"/>
+      <x:c r="G3" s="8"/>
+      <x:c r="H3" s="8"/>
+      <x:c r="I3" s="8"/>
+      <x:c r="J3" s="8"/>
+      <x:c r="K3" s="8"/>
+      <x:c r="L3" s="8"/>
       <x:c r="M3" s="8" t="str">
         <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='conversion.calculate',input_category='length',return_mode='flat',input_payload_mode='FULL')</x:v>
       </x:c>
@@ -383,128 +383,130 @@
       <x:c r="C4" s="8" t="str">
         <x:v>Value</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="str"/>
-      <x:c r="E4" s="8" t="str"/>
+      <x:c r="D4" s="8"/>
+      <x:c r="E4" s="8"/>
       <x:c r="F4" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G4" s="8" t="str"/>
-      <x:c r="H4" s="8" t="str"/>
-      <x:c r="I4" s="8" t="str"/>
-      <x:c r="J4" s="8" t="str"/>
-      <x:c r="K4" s="8" t="str"/>
-      <x:c r="L4" s="8" t="str"/>
-      <x:c r="M4" s="8" t="str"/>
+      <x:c r="G4" s="8"/>
+      <x:c r="H4" s="8"/>
+      <x:c r="I4" s="8"/>
+      <x:c r="J4" s="8"/>
+      <x:c r="K4" s="8"/>
+      <x:c r="L4" s="8"/>
+      <x:c r="M4" s="8"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="8" t="str">
-        <x:v>text</x:v>
+        <x:v>integer</x:v>
       </x:c>
       <x:c r="B5" s="8" t="str">
-        <x:v>input_from_unit</x:v>
+        <x:v>input_decimal_places</x:v>
       </x:c>
       <x:c r="C5" s="8" t="str">
-        <x:v>From unit (for example m)</x:v>
-      </x:c>
-      <x:c r="D5" s="8" t="str"/>
-      <x:c r="E5" s="8" t="str"/>
-      <x:c r="F5" s="8" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="G5" s="8" t="str"/>
-      <x:c r="H5" s="8" t="str"/>
-      <x:c r="I5" s="8" t="str"/>
-      <x:c r="J5" s="8" t="str"/>
-      <x:c r="K5" s="8" t="str"/>
-      <x:c r="L5" s="8" t="str"/>
-      <x:c r="M5" s="8" t="str"/>
+        <x:v>Decimal places</x:v>
+      </x:c>
+      <x:c r="D5" s="8" t="str">
+        <x:v>0–10; defaults to 4</x:v>
+      </x:c>
+      <x:c r="E5" s="8"/>
+      <x:c r="F5" s="8"/>
+      <x:c r="G5" s="8"/>
+      <x:c r="H5" s="8" t="str">
+        <x:v>. &gt;= 0 and . &lt;= 10</x:v>
+      </x:c>
+      <x:c r="I5" s="8" t="str">
+        <x:v>Enter a value from 0 to 10.</x:v>
+      </x:c>
+      <x:c r="J5" s="8"/>
+      <x:c r="K5" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="L5" s="8"/>
+      <x:c r="M5" s="8"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B6" s="8" t="str">
-        <x:v>input_to_unit</x:v>
+        <x:v>input_from_unit</x:v>
       </x:c>
       <x:c r="C6" s="8" t="str">
-        <x:v>To unit (for example km)</x:v>
-      </x:c>
-      <x:c r="D6" s="8" t="str"/>
-      <x:c r="E6" s="8" t="str"/>
+        <x:v>From unit (for example m)</x:v>
+      </x:c>
+      <x:c r="D6" s="8"/>
+      <x:c r="E6" s="8"/>
       <x:c r="F6" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G6" s="8" t="str"/>
-      <x:c r="H6" s="8" t="str"/>
-      <x:c r="I6" s="8" t="str"/>
-      <x:c r="J6" s="8" t="str"/>
-      <x:c r="K6" s="8" t="str"/>
-      <x:c r="L6" s="8" t="str"/>
-      <x:c r="M6" s="8" t="str"/>
+      <x:c r="G6" s="8"/>
+      <x:c r="H6" s="8"/>
+      <x:c r="I6" s="8"/>
+      <x:c r="J6" s="8"/>
+      <x:c r="K6" s="8"/>
+      <x:c r="L6" s="8"/>
+      <x:c r="M6" s="8"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B7" s="8" t="str">
-        <x:v>methodmesh_status</x:v>
+        <x:v>input_to_unit</x:v>
       </x:c>
       <x:c r="C7" s="8" t="str">
-        <x:v>Methodmesh Status</x:v>
-      </x:c>
-      <x:c r="D7" s="8" t="str">
-        <x:v>Shared MethodMesh transport status, where projected by the runtime.</x:v>
-      </x:c>
-      <x:c r="E7" s="8" t="str">
-        <x:v>hidden-answer</x:v>
-      </x:c>
-      <x:c r="F7" s="8" t="str"/>
-      <x:c r="G7" s="8" t="str"/>
-      <x:c r="H7" s="8" t="str"/>
-      <x:c r="I7" s="8" t="str"/>
-      <x:c r="J7" s="8" t="str"/>
-      <x:c r="K7" s="8" t="str"/>
-      <x:c r="L7" s="8" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="M7" s="8" t="str"/>
+        <x:v>To unit (for example km)</x:v>
+      </x:c>
+      <x:c r="D7" s="8"/>
+      <x:c r="E7" s="8"/>
+      <x:c r="F7" s="8" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G7" s="8"/>
+      <x:c r="H7" s="8"/>
+      <x:c r="I7" s="8"/>
+      <x:c r="J7" s="8"/>
+      <x:c r="K7" s="8"/>
+      <x:c r="L7" s="8"/>
+      <x:c r="M7" s="8"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B8" s="8" t="str">
-        <x:v>conversion_value</x:v>
+        <x:v>methodmesh_status</x:v>
       </x:c>
       <x:c r="C8" s="8" t="str">
-        <x:v>Converted value</x:v>
+        <x:v>Methodmesh Status</x:v>
       </x:c>
       <x:c r="D8" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
+        <x:v>Shared MethodMesh transport status, where projected by the runtime.</x:v>
       </x:c>
       <x:c r="E8" s="8" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F8" s="8" t="str"/>
-      <x:c r="G8" s="8" t="str"/>
-      <x:c r="H8" s="8" t="str"/>
-      <x:c r="I8" s="8" t="str"/>
-      <x:c r="J8" s="8" t="str"/>
-      <x:c r="K8" s="8" t="str"/>
+      <x:c r="F8" s="8"/>
+      <x:c r="G8" s="8"/>
+      <x:c r="H8" s="8"/>
+      <x:c r="I8" s="8"/>
+      <x:c r="J8" s="8"/>
+      <x:c r="K8" s="8"/>
       <x:c r="L8" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M8" s="8" t="str"/>
+      <x:c r="M8" s="8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B9" s="8" t="str">
-        <x:v>conversion_unit</x:v>
+        <x:v>conversion_value</x:v>
       </x:c>
       <x:c r="C9" s="8" t="str">
-        <x:v>Output unit</x:v>
+        <x:v>Converted value</x:v>
       </x:c>
       <x:c r="D9" s="8" t="str">
         <x:v>Returned by MethodMesh.</x:v>
@@ -512,26 +514,26 @@
       <x:c r="E9" s="8" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F9" s="8" t="str"/>
-      <x:c r="G9" s="8" t="str"/>
-      <x:c r="H9" s="8" t="str"/>
-      <x:c r="I9" s="8" t="str"/>
-      <x:c r="J9" s="8" t="str"/>
-      <x:c r="K9" s="8" t="str"/>
+      <x:c r="F9" s="8"/>
+      <x:c r="G9" s="8"/>
+      <x:c r="H9" s="8"/>
+      <x:c r="I9" s="8"/>
+      <x:c r="J9" s="8"/>
+      <x:c r="K9" s="8"/>
       <x:c r="L9" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M9" s="8" t="str"/>
+      <x:c r="M9" s="8"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B10" s="8" t="str">
-        <x:v>conversion_summary</x:v>
+        <x:v>conversion_unit</x:v>
       </x:c>
       <x:c r="C10" s="8" t="str">
-        <x:v>Summary</x:v>
+        <x:v>Output unit</x:v>
       </x:c>
       <x:c r="D10" s="8" t="str">
         <x:v>Returned by MethodMesh.</x:v>
@@ -539,26 +541,26 @@
       <x:c r="E10" s="8" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F10" s="8" t="str"/>
-      <x:c r="G10" s="8" t="str"/>
-      <x:c r="H10" s="8" t="str"/>
-      <x:c r="I10" s="8" t="str"/>
-      <x:c r="J10" s="8" t="str"/>
-      <x:c r="K10" s="8" t="str"/>
+      <x:c r="F10" s="8"/>
+      <x:c r="G10" s="8"/>
+      <x:c r="H10" s="8"/>
+      <x:c r="I10" s="8"/>
+      <x:c r="J10" s="8"/>
+      <x:c r="K10" s="8"/>
       <x:c r="L10" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M10" s="8" t="str"/>
+      <x:c r="M10" s="8"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B11" s="8" t="str">
-        <x:v>conversion_status</x:v>
+        <x:v>conversion_summary</x:v>
       </x:c>
       <x:c r="C11" s="8" t="str">
-        <x:v>Status</x:v>
+        <x:v>Summary</x:v>
       </x:c>
       <x:c r="D11" s="8" t="str">
         <x:v>Returned by MethodMesh.</x:v>
@@ -566,26 +568,26 @@
       <x:c r="E11" s="8" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F11" s="8" t="str"/>
-      <x:c r="G11" s="8" t="str"/>
-      <x:c r="H11" s="8" t="str"/>
-      <x:c r="I11" s="8" t="str"/>
-      <x:c r="J11" s="8" t="str"/>
-      <x:c r="K11" s="8" t="str"/>
+      <x:c r="F11" s="8"/>
+      <x:c r="G11" s="8"/>
+      <x:c r="H11" s="8"/>
+      <x:c r="I11" s="8"/>
+      <x:c r="J11" s="8"/>
+      <x:c r="K11" s="8"/>
       <x:c r="L11" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M11" s="8" t="str"/>
+      <x:c r="M11" s="8"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B12" s="8" t="str">
-        <x:v>conversion_error</x:v>
+        <x:v>conversion_status</x:v>
       </x:c>
       <x:c r="C12" s="8" t="str">
-        <x:v>Error</x:v>
+        <x:v>Status</x:v>
       </x:c>
       <x:c r="D12" s="8" t="str">
         <x:v>Returned by MethodMesh.</x:v>
@@ -593,83 +595,137 @@
       <x:c r="E12" s="8" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F12" s="8" t="str"/>
-      <x:c r="G12" s="8" t="str"/>
-      <x:c r="H12" s="8" t="str"/>
-      <x:c r="I12" s="8" t="str"/>
-      <x:c r="J12" s="8" t="str"/>
-      <x:c r="K12" s="8" t="str"/>
+      <x:c r="F12" s="8"/>
+      <x:c r="G12" s="8"/>
+      <x:c r="H12" s="8"/>
+      <x:c r="I12" s="8"/>
+      <x:c r="J12" s="8"/>
+      <x:c r="K12" s="8"/>
       <x:c r="L12" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M12" s="8" t="str"/>
+      <x:c r="M12" s="8"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B13" s="8" t="str">
-        <x:v>methodmesh_full_json</x:v>
+        <x:v>conversion_error</x:v>
       </x:c>
       <x:c r="C13" s="8" t="str">
-        <x:v>Methodmesh Full Json</x:v>
+        <x:v>Error</x:v>
       </x:c>
       <x:c r="D13" s="8" t="str">
-        <x:v>Shared MethodMesh FULL execution envelope. Retained for complete execution/audit capture; capability-specific return fields are projected separately.</x:v>
+        <x:v>Returned by MethodMesh.</x:v>
       </x:c>
       <x:c r="E13" s="8" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F13" s="8" t="str"/>
-      <x:c r="G13" s="8" t="str"/>
-      <x:c r="H13" s="8" t="str"/>
-      <x:c r="I13" s="8" t="str"/>
-      <x:c r="J13" s="8" t="str"/>
-      <x:c r="K13" s="8" t="str"/>
+      <x:c r="F13" s="8"/>
+      <x:c r="G13" s="8"/>
+      <x:c r="H13" s="8"/>
+      <x:c r="I13" s="8"/>
+      <x:c r="J13" s="8"/>
+      <x:c r="K13" s="8"/>
       <x:c r="L13" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M13" s="8" t="str"/>
+      <x:c r="M13" s="8"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="8" t="str">
-        <x:v>end_group</x:v>
-      </x:c>
-      <x:c r="B14" s="8" t="str"/>
-      <x:c r="C14" s="8" t="str"/>
-      <x:c r="D14" s="8" t="str"/>
-      <x:c r="E14" s="8" t="str"/>
-      <x:c r="F14" s="8" t="str"/>
-      <x:c r="G14" s="8" t="str"/>
-      <x:c r="H14" s="8" t="str"/>
-      <x:c r="I14" s="8" t="str"/>
-      <x:c r="J14" s="8" t="str"/>
-      <x:c r="K14" s="8" t="str"/>
-      <x:c r="L14" s="8" t="str"/>
-      <x:c r="M14" s="8" t="str"/>
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B14" s="8" t="str">
+        <x:v>conversion_metadata_json</x:v>
+      </x:c>
+      <x:c r="C14" s="8" t="str">
+        <x:v>Conversion metadata JSON</x:v>
+      </x:c>
+      <x:c r="D14" s="8" t="str">
+        <x:v>Capability-declared structured metadata returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E14" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F14" s="8"/>
+      <x:c r="G14" s="8"/>
+      <x:c r="H14" s="8"/>
+      <x:c r="I14" s="8"/>
+      <x:c r="J14" s="8"/>
+      <x:c r="K14" s="8"/>
+      <x:c r="L14" s="8" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="M14" s="8"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B15" s="8" t="str">
+        <x:v>methodmesh_full_json</x:v>
+      </x:c>
+      <x:c r="C15" s="8" t="str">
+        <x:v>Methodmesh Full Json</x:v>
+      </x:c>
+      <x:c r="D15" s="8" t="str">
+        <x:v>Shared MethodMesh FULL execution envelope. Retained for complete execution/audit capture; capability-specific return fields are projected separately.</x:v>
+      </x:c>
+      <x:c r="E15" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F15" s="8"/>
+      <x:c r="G15" s="8"/>
+      <x:c r="H15" s="8"/>
+      <x:c r="I15" s="8"/>
+      <x:c r="J15" s="8"/>
+      <x:c r="K15" s="8"/>
+      <x:c r="L15" s="8" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="M15" s="8"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>end_group</x:v>
+      </x:c>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
+      <x:c r="M16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
         <x:v>note</x:v>
       </x:c>
-      <x:c r="B15" s="8" t="str">
+      <x:c r="B17" t="str">
         <x:v>return_summary</x:v>
       </x:c>
-      <x:c r="C15" s="8" t="str">
+      <x:c r="C17" t="str">
         <x:v>MethodMesh return captured. Status: ${methodmesh_status}</x:v>
       </x:c>
-      <x:c r="D15" s="8" t="str">
+      <x:c r="D17" t="str">
         <x:v>Only fields relevant to this capability are stored, plus the shared FULL envelope.</x:v>
       </x:c>
-      <x:c r="E15" s="8" t="str"/>
-      <x:c r="F15" s="8" t="str"/>
-      <x:c r="G15" s="8" t="str"/>
-      <x:c r="H15" s="8" t="str"/>
-      <x:c r="I15" s="8" t="str"/>
-      <x:c r="J15" s="8" t="str"/>
-      <x:c r="K15" s="8" t="str"/>
-      <x:c r="L15" s="8" t="str"/>
-      <x:c r="M15" s="8" t="str"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
+      <x:c r="H17"/>
+      <x:c r="I17"/>
+      <x:c r="J17"/>
+      <x:c r="K17"/>
+      <x:c r="L17"/>
+      <x:c r="M17"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
